--- a/课程.xlsx
+++ b/课程.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t>章节</t>
   </si>
@@ -61,6 +61,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>Python</t>
     </r>
     <r>
@@ -72,6 +78,9 @@
       </rPr>
       <t>常用数据类型</t>
     </r>
+  </si>
+  <si>
+    <t>Python面向对象</t>
   </si>
   <si>
     <t>走进人工智能</t>
@@ -771,7 +780,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -795,6 +804,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1107,8 +1119,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4"/>
+  <dimension ref="A1:A6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="1" width="35.1111111111111" customWidth="1"/>
   </cols>
@@ -1136,6 +1148,11 @@
     <row r="5" spans="1:1">
       <c r="A5" s="6" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="6" ht="15.6" spans="1:1">
+      <c r="A6" s="8" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1161,47 +1178,47 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/课程.xlsx
+++ b/课程.xlsx
@@ -4,12 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060"/>
+    <workbookView windowWidth="23040" windowHeight="9060" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="程序设计基础（Python）" sheetId="1" r:id="rId1"/>
     <sheet name="人工智能应用导论" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t>章节</t>
   </si>
@@ -81,6 +80,12 @@
   </si>
   <si>
     <t>Python面向对象</t>
+  </si>
+  <si>
+    <t>Python文件操作</t>
+  </si>
+  <si>
+    <t>Python数据库操作</t>
   </si>
   <si>
     <t>走进人工智能</t>
@@ -780,7 +785,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -805,8 +810,14 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1119,8 +1130,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="35.1111111111111" customWidth="1"/>
   </cols>
@@ -1153,6 +1164,16 @@
     <row r="6" ht="15.6" spans="1:1">
       <c r="A6" s="8" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="10" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1178,47 +1199,47 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1226,16 +1247,4 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/课程.xlsx
+++ b/课程.xlsx
@@ -4,11 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="9060" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="程序设计基础（Python）" sheetId="1" r:id="rId1"/>
     <sheet name="人工智能应用导论" sheetId="2" r:id="rId2"/>
+    <sheet name="信息技术" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
   <si>
     <t>章节</t>
   </si>
@@ -113,6 +114,39 @@
   </si>
   <si>
     <t>机器学习代码生成</t>
+  </si>
+  <si>
+    <t>文档的格式设置</t>
+  </si>
+  <si>
+    <t>文档的图文混排</t>
+  </si>
+  <si>
+    <t>文档中表格应用</t>
+  </si>
+  <si>
+    <t>长文档排版</t>
+  </si>
+  <si>
+    <t>表格的制作</t>
+  </si>
+  <si>
+    <t>表格数据的整理与优化</t>
+  </si>
+  <si>
+    <t>表格数据的图表显示</t>
+  </si>
+  <si>
+    <t>表格数据的进阶处理</t>
+  </si>
+  <si>
+    <t>制作"个人简介"演示文稿</t>
+  </si>
+  <si>
+    <t>设置演示文稿动画</t>
+  </si>
+  <si>
+    <t>优化演示文稿</t>
   </si>
 </sst>
 </file>
@@ -790,6 +824,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -815,9 +852,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1137,42 +1171,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" ht="15.6" spans="1:1">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="8" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="7" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="7" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" ht="15.6" spans="1:1">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="10" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1193,52 +1227,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="5" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1247,4 +1281,79 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A12"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="22.1111111111111" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/课程.xlsx
+++ b/课程.xlsx
@@ -4,12 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060" activeTab="2"/>
+    <workbookView windowWidth="23040" windowHeight="9060" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="程序设计基础（Python）" sheetId="1" r:id="rId1"/>
     <sheet name="人工智能应用导论" sheetId="2" r:id="rId2"/>
     <sheet name="信息技术" sheetId="3" r:id="rId3"/>
+    <sheet name="认识实习" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1356,4 +1357,15 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/课程.xlsx
+++ b/课程.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
   <si>
     <t>章节</t>
   </si>
@@ -148,6 +148,21 @@
   </si>
   <si>
     <t>优化演示文稿</t>
+  </si>
+  <si>
+    <t>星期一</t>
+  </si>
+  <si>
+    <t>星期二</t>
+  </si>
+  <si>
+    <t>星期三</t>
+  </si>
+  <si>
+    <t>星期四</t>
+  </si>
+  <si>
+    <t>星期五</t>
   </si>
 </sst>
 </file>
@@ -1362,9 +1377,35 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="4"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/课程.xlsx
+++ b/课程.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
   <si>
     <t>章节</t>
   </si>
@@ -1377,31 +1377,36 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="4"/>
+  <dimension ref="A1:A6"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="5"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
         <v>32</v>
       </c>
     </row>
